--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -821,10 +821,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119657801</v>
+        <v>119657304</v>
       </c>
       <c r="B3" t="n">
-        <v>96862</v>
+        <v>97928</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,26 +837,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -869,10 +881,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504852</v>
+        <v>504838</v>
       </c>
       <c r="R3" t="n">
-        <v>7007539</v>
+        <v>7007557</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,6 +917,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Minst 4 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,10 +959,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119656913</v>
+        <v>119651220</v>
       </c>
       <c r="B4" t="n">
-        <v>96862</v>
+        <v>97813</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,16 +975,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -975,9 +992,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -986,14 +1015,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Granskog vid Åsens vägskäl, Jmt</t>
+          <t>Åsens vägskäl, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504831</v>
+        <v>504816</v>
       </c>
       <c r="R4" t="n">
-        <v>7007540</v>
+        <v>7007549</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1030,7 +1059,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Måttlig förekomst av revlummer. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>9 st. skott/stjälkar av guckusko med minst 1 st överblommad blomstängel som här växer i dikeskanten. När gräs och örter slagits i dikesområdet har flera av guckuskons stjälkar skadats. Här finns även fler orkidéarter. Obs! denna fyndplats ligger även inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,12 +1074,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
+          <t>Vägkant intill dike med fältskikt av gräs och örter varav flera orkidéarter på frisk och frisk-fuktig kalkhaltig mark intill äldre granskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1068,10 +1097,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119657398</v>
+        <v>119657801</v>
       </c>
       <c r="B5" t="n">
-        <v>97928</v>
+        <v>96862</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1084,38 +1113,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -1164,11 +1181,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 2 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1206,10 +1218,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119656872</v>
+        <v>119656053</v>
       </c>
       <c r="B6" t="n">
-        <v>97824</v>
+        <v>97909</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1222,26 +1234,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1251,7 +1263,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1262,14 +1274,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Granskog vid Åsens vägskäl, Jmt</t>
+          <t>Åsens vägskäl, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504831</v>
+        <v>504816</v>
       </c>
       <c r="R6" t="n">
-        <v>7007540</v>
+        <v>7007549</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1306,7 +1318,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst ett skott av fläcknycklar med en överblommad kort blomställning. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst 4 st. skott/stjälkar av brudsporre där alla stjälkar har överblommade blomstänglar som här växer i dikeskanten intill en landsväg. På och intill fyndplatsen finns även fler orkidéarter. Obs! denna fyndplats ligger även inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1321,12 +1333,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
+          <t>Vägkant intill dike med fältskikt av gräs och örter varav flera orkidéarter på frisk och frisk-fuktig kalkhaltig mark intill äldre granskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1344,10 +1356,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119656053</v>
+        <v>119656913</v>
       </c>
       <c r="B7" t="n">
-        <v>97909</v>
+        <v>96862</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1360,38 +1372,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219811</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
@@ -1400,14 +1400,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åsens vägskäl, Jmt</t>
+          <t>Granskog vid Åsens vägskäl, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504816</v>
+        <v>504831</v>
       </c>
       <c r="R7" t="n">
-        <v>7007549</v>
+        <v>7007540</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 4 st. skott/stjälkar av brudsporre där alla stjälkar har överblommade blomstänglar som här växer i dikeskanten intill en landsväg. På och intill fyndplatsen finns även fler orkidéarter. Obs! denna fyndplats ligger även inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Måttlig förekomst av revlummer. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Vägkant intill dike med fältskikt av gräs och örter varav flera orkidéarter på frisk och frisk-fuktig kalkhaltig mark intill äldre granskog.</t>
+          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651220</v>
+        <v>119657228</v>
       </c>
       <c r="B8" t="n">
-        <v>97813</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1498,26 +1498,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1538,14 +1538,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åsens vägskäl, Jmt</t>
+          <t>Granskog vid Åsens vägskäl, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504816</v>
+        <v>504838</v>
       </c>
       <c r="R8" t="n">
-        <v>7007549</v>
+        <v>7007557</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>9 st. skott/stjälkar av guckusko med minst 1 st överblommad blomstängel som här växer i dikeskanten. När gräs och örter slagits i dikesområdet har flera av guckuskons stjälkar skadats. Här finns även fler orkidéarter. Obs! denna fyndplats ligger även inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst ett skott av tvåblad. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Vägkant intill dike med fältskikt av gräs och örter varav flera orkidéarter på frisk och frisk-fuktig kalkhaltig mark intill äldre granskog.</t>
+          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119657304</v>
+        <v>119656872</v>
       </c>
       <c r="B9" t="n">
-        <v>97928</v>
+        <v>97824</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1636,26 +1636,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504838</v>
+        <v>504831</v>
       </c>
       <c r="R9" t="n">
-        <v>7007557</v>
+        <v>7007540</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 4 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst ett skott av fläcknycklar med en överblommad kort blomställning. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1758,10 +1758,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119657228</v>
+        <v>119657398</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>97928</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1774,26 +1774,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504838</v>
+        <v>504852</v>
       </c>
       <c r="R10" t="n">
-        <v>7007557</v>
+        <v>7007539</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst ett skott av tvåblad. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst 2 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -959,10 +959,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651220</v>
+        <v>119656872</v>
       </c>
       <c r="B4" t="n">
-        <v>97813</v>
+        <v>97824</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,26 +975,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>504</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1015,14 +1015,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åsens vägskäl, Jmt</t>
+          <t>Granskog vid Åsens vägskäl, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504816</v>
+        <v>504831</v>
       </c>
       <c r="R4" t="n">
-        <v>7007549</v>
+        <v>7007540</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>9 st. skott/stjälkar av guckusko med minst 1 st överblommad blomstängel som här växer i dikeskanten. När gräs och örter slagits i dikesområdet har flera av guckuskons stjälkar skadats. Här finns även fler orkidéarter. Obs! denna fyndplats ligger även inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst ett skott av fläcknycklar med en överblommad kort blomställning. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Vägkant intill dike med fältskikt av gräs och örter varav flera orkidéarter på frisk och frisk-fuktig kalkhaltig mark intill äldre granskog.</t>
+          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119657801</v>
+        <v>119657398</v>
       </c>
       <c r="B5" t="n">
-        <v>96862</v>
+        <v>97928</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1113,26 +1113,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -1181,6 +1193,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 2 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1218,10 +1235,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119656053</v>
+        <v>119651220</v>
       </c>
       <c r="B6" t="n">
-        <v>97909</v>
+        <v>97813</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1234,26 +1251,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219811</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1263,7 +1280,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1318,7 +1335,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 4 st. skott/stjälkar av brudsporre där alla stjälkar har överblommade blomstänglar som här växer i dikeskanten intill en landsväg. På och intill fyndplatsen finns även fler orkidéarter. Obs! denna fyndplats ligger även inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>9 st. skott/stjälkar av guckusko med minst 1 st överblommad blomstängel som här växer i dikeskanten. När gräs och örter slagits i dikesområdet har flera av guckuskons stjälkar skadats. Här finns även fler orkidéarter. Obs! denna fyndplats ligger även inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1356,10 +1373,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119656913</v>
+        <v>119657228</v>
       </c>
       <c r="B7" t="n">
-        <v>96862</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1372,26 +1389,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
@@ -1404,10 +1433,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504831</v>
+        <v>504838</v>
       </c>
       <c r="R7" t="n">
-        <v>7007540</v>
+        <v>7007557</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1444,7 +1473,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Måttlig förekomst av revlummer. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst ett skott av tvåblad. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1482,10 +1511,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119657228</v>
+        <v>119656913</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>96862</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1498,38 +1527,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
@@ -1542,10 +1559,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504838</v>
+        <v>504831</v>
       </c>
       <c r="R8" t="n">
-        <v>7007557</v>
+        <v>7007540</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1582,7 +1599,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst ett skott av tvåblad. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Måttlig förekomst av revlummer. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1620,10 +1637,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119656872</v>
+        <v>119657801</v>
       </c>
       <c r="B9" t="n">
-        <v>97824</v>
+        <v>96862</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1636,38 +1653,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
@@ -1680,10 +1685,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504831</v>
+        <v>504852</v>
       </c>
       <c r="R9" t="n">
-        <v>7007540</v>
+        <v>7007539</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1716,11 +1721,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst ett skott av fläcknycklar med en överblommad kort blomställning. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1758,10 +1758,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119657398</v>
+        <v>119656053</v>
       </c>
       <c r="B10" t="n">
-        <v>97928</v>
+        <v>97909</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1774,26 +1774,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>219811</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1814,14 +1814,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granskog vid Åsens vägskäl, Jmt</t>
+          <t>Åsens vägskäl, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504852</v>
+        <v>504816</v>
       </c>
       <c r="R10" t="n">
-        <v>7007539</v>
+        <v>7007549</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 2 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst 4 st. skott/stjälkar av brudsporre där alla stjälkar har överblommade blomstänglar som här växer i dikeskanten intill en landsväg. På och intill fyndplatsen finns även fler orkidéarter. Obs! denna fyndplats ligger även inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
+          <t>Vägkant intill dike med fältskikt av gräs och örter varav flera orkidéarter på frisk och frisk-fuktig kalkhaltig mark intill äldre granskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -821,10 +821,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119657304</v>
+        <v>119656872</v>
       </c>
       <c r="B3" t="n">
-        <v>97928</v>
+        <v>97824</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,26 +837,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504838</v>
+        <v>504831</v>
       </c>
       <c r="R3" t="n">
-        <v>7007557</v>
+        <v>7007540</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -921,7 +921,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 4 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst ett skott av fläcknycklar med en överblommad kort blomställning. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -959,10 +959,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119656872</v>
+        <v>119657304</v>
       </c>
       <c r="B4" t="n">
-        <v>97824</v>
+        <v>97928</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,26 +975,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504831</v>
+        <v>504838</v>
       </c>
       <c r="R4" t="n">
-        <v>7007540</v>
+        <v>7007557</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst ett skott av fläcknycklar med en överblommad kort blomställning. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst 4 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -821,10 +821,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119656872</v>
+        <v>119657398</v>
       </c>
       <c r="B3" t="n">
-        <v>97824</v>
+        <v>97928</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,26 +837,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504831</v>
+        <v>504852</v>
       </c>
       <c r="R3" t="n">
-        <v>7007540</v>
+        <v>7007539</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -921,7 +921,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst ett skott av fläcknycklar med en överblommad kort blomställning. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst 2 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1097,10 +1097,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119657398</v>
+        <v>119656053</v>
       </c>
       <c r="B5" t="n">
-        <v>97928</v>
+        <v>97909</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1113,26 +1113,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1153,14 +1153,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Granskog vid Åsens vägskäl, Jmt</t>
+          <t>Åsens vägskäl, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504852</v>
+        <v>504816</v>
       </c>
       <c r="R5" t="n">
-        <v>7007539</v>
+        <v>7007549</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 2 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst 4 st. skott/stjälkar av brudsporre där alla stjälkar har överblommade blomstänglar som här växer i dikeskanten intill en landsväg. På och intill fyndplatsen finns även fler orkidéarter. Obs! denna fyndplats ligger även inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
+          <t>Vägkant intill dike med fältskikt av gräs och örter varav flera orkidéarter på frisk och frisk-fuktig kalkhaltig mark intill äldre granskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119657228</v>
+        <v>119656913</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>96862</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1389,38 +1389,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
@@ -1433,10 +1421,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504838</v>
+        <v>504831</v>
       </c>
       <c r="R7" t="n">
-        <v>7007557</v>
+        <v>7007540</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1473,7 +1461,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst ett skott av tvåblad. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Måttlig förekomst av revlummer. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1511,10 +1499,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119656913</v>
+        <v>119657228</v>
       </c>
       <c r="B8" t="n">
-        <v>96862</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1527,26 +1515,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504831</v>
+        <v>504838</v>
       </c>
       <c r="R8" t="n">
-        <v>7007540</v>
+        <v>7007557</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Måttlig förekomst av revlummer. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst ett skott av tvåblad. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1637,10 +1637,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119657801</v>
+        <v>119656872</v>
       </c>
       <c r="B9" t="n">
-        <v>96862</v>
+        <v>97824</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1653,26 +1653,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
@@ -1685,10 +1697,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504852</v>
+        <v>504831</v>
       </c>
       <c r="R9" t="n">
-        <v>7007539</v>
+        <v>7007540</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1721,6 +1733,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst ett skott av fläcknycklar med en överblommad kort blomställning. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1758,10 +1775,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119656053</v>
+        <v>119657801</v>
       </c>
       <c r="B10" t="n">
-        <v>97909</v>
+        <v>96862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1774,38 +1791,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219811</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
@@ -1814,14 +1819,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åsens vägskäl, Jmt</t>
+          <t>Granskog vid Åsens vägskäl, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504816</v>
+        <v>504852</v>
       </c>
       <c r="R10" t="n">
-        <v>7007549</v>
+        <v>7007539</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1856,11 +1861,6 @@
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 4 st. skott/stjälkar av brudsporre där alla stjälkar har överblommade blomstänglar som här växer i dikeskanten intill en landsväg. På och intill fyndplatsen finns även fler orkidéarter. Obs! denna fyndplats ligger även inom en avverkningsanmälan med beteckning A 7710-2024.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Vägkant intill dike med fältskikt av gräs och örter varav flera orkidéarter på frisk och frisk-fuktig kalkhaltig mark intill äldre granskog.</t>
+          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,65 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115107303</v>
+        <v>119651220</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granskog vid Åsens vägskäl, Jmt</t>
+          <t>Åsens vägskäl, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504825</v>
+        <v>504816</v>
       </c>
       <c r="R2" t="n">
-        <v>7007501</v>
+        <v>7007549</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,17 +760,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Enstaka bålar av långväxt garnlav på gran intill andra hänglavar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>9 st. skott/stjälkar av guckusko med minst 1 st överblommad blomstängel som här växer i dikeskanten. När gräs och örter slagits i dikesområdet har flera av guckuskons stjälkar skadats. Här finns även fler orkidéarter. Obs! denna fyndplats ligger även inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,37 +785,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>En gran som står i en luckig del av skogsbeståndet.</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torra döda grenar på en levande gran. # Picea abies # En gran som står i en luckig del av skogsbeståndet.</t>
+          <t>Vägkant intill dike med fältskikt av gräs och örter varav flera orkidéarter på frisk och frisk-fuktig kalkhaltig mark intill äldre granskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -821,70 +808,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119657398</v>
+        <v>115107303</v>
       </c>
       <c r="B3" t="n">
-        <v>97928</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granskog vid Åsens vägskäl, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504852</v>
+        <v>504825</v>
       </c>
       <c r="R3" t="n">
-        <v>7007539</v>
+        <v>7007501</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -911,17 +876,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 2 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Enstaka bålar av långväxt garnlav på gran intill andra hänglavar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,6 +907,31 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>En gran som står i en luckig del av skogsbeståndet.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torra döda grenar på en levande gran. # Picea abies # En gran som står i en luckig del av skogsbeståndet.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -959,55 +949,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119657304</v>
+        <v>119662301</v>
       </c>
       <c r="B4" t="n">
-        <v>97928</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1015,17 +996,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Granskog vid Åsens vägskäl, Jmt</t>
+          <t>Granskog vid Åsens vägskäl, Hålmyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504838</v>
+        <v>504835</v>
       </c>
       <c r="R4" t="n">
-        <v>7007557</v>
+        <v>7007531</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1059,7 +1040,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 4 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Observation av lätet från minst en talltita. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,7 +1049,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1097,15 +1077,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119656053</v>
+        <v>119656872</v>
       </c>
       <c r="B5" t="n">
-        <v>97909</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,26 +1088,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1142,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1153,14 +1128,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åsens vägskäl, Jmt</t>
+          <t>Granskog vid Åsens vägskäl, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504816</v>
+        <v>504831</v>
       </c>
       <c r="R5" t="n">
-        <v>7007549</v>
+        <v>7007540</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1197,7 +1172,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 4 st. skott/stjälkar av brudsporre där alla stjälkar har överblommade blomstänglar som här växer i dikeskanten intill en landsväg. På och intill fyndplatsen finns även fler orkidéarter. Obs! denna fyndplats ligger även inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst ett skott av fläcknycklar med en överblommad kort blomställning. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1212,12 +1187,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Vägkant intill dike med fältskikt av gräs och örter varav flera orkidéarter på frisk och frisk-fuktig kalkhaltig mark intill äldre granskog.</t>
+          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1235,15 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119651220</v>
+        <v>119656053</v>
       </c>
       <c r="B6" t="n">
-        <v>97813</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,26 +1221,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>504</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1280,7 +1250,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1335,7 +1305,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>9 st. skott/stjälkar av guckusko med minst 1 st överblommad blomstängel som här växer i dikeskanten. När gräs och örter slagits i dikesområdet har flera av guckuskons stjälkar skadats. Här finns även fler orkidéarter. Obs! denna fyndplats ligger även inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst 4 st. skott/stjälkar av brudsporre där alla stjälkar har överblommade blomstänglar som här växer i dikeskanten intill en landsväg. På och intill fyndplatsen finns även fler orkidéarter. Obs! denna fyndplats ligger även inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1373,15 +1343,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119656913</v>
+        <v>119656618</v>
       </c>
       <c r="B7" t="n">
-        <v>96862</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,26 +1354,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>219811</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
@@ -1417,14 +1394,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Granskog vid Åsens vägskäl, Jmt</t>
+          <t>Åsens vägskäl, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504831</v>
+        <v>504820</v>
       </c>
       <c r="R7" t="n">
-        <v>7007540</v>
+        <v>7007565</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1461,7 +1438,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Måttlig förekomst av revlummer. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst 5 st. skott/stjälkar av brudsporre där alla stjälkar har överblommade blomstänglar som här växer i dikeskanten intill en landsväg. Intill fyndplatsen finns även fler orkidéarter. Obs! Denna fyndplats påverkas av att vegetationen i dikeskanten slås och den ligger även ca 5 meter från en avverkningsanmälan med beteckning A 7710-2024</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1476,12 +1453,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
+          <t>Vägkant intill dike med fältskikt av gräs och örter varav flera orkidéarter på frisk och frisk-fuktig kalkhaltig mark intill äldre granskog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1502,12 +1479,7 @@
         <v>119657228</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1637,15 +1609,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119656872</v>
+        <v>119656913</v>
       </c>
       <c r="B9" t="n">
-        <v>97824</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1653,38 +1620,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
@@ -1737,7 +1692,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst ett skott av fläcknycklar med en överblommad kort blomställning. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Måttlig förekomst av revlummer. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1778,12 +1733,7 @@
         <v>119657801</v>
       </c>
       <c r="B10" t="n">
-        <v>96862</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1896,51 +1846,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119662301</v>
+        <v>119657304</v>
       </c>
       <c r="B11" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1948,17 +1897,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Granskog vid Åsens vägskäl, Hålmyren, Lit, Jmt</t>
+          <t>Granskog vid Åsens vägskäl, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504835</v>
+        <v>504838</v>
       </c>
       <c r="R11" t="n">
-        <v>7007531</v>
+        <v>7007557</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1992,7 +1941,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Observation av lätet från minst en talltita. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst 4 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2001,6 +1950,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2026,6 +1976,139 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>119657398</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Granskog vid Åsens vägskäl, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>504852</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7007539</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 2 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -805,6 +810,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651220</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -946,6 +956,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107303</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1074,6 +1089,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119662301</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1207,6 +1227,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119656872</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1340,6 +1365,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119656053</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1473,6 +1503,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119656618</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1606,6 +1641,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119657228</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1727,6 +1767,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119656913</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1843,6 +1888,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119657801</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1976,6 +2026,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119657304</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2109,8 +2164,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119657398</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>